--- a/data/trans_camb/IP2002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 5,6</t>
+          <t>-12,31; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 11,17</t>
+          <t>-8,14; 11,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 8,41</t>
+          <t>-10,59; 8,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 16,68</t>
+          <t>-3,85; 16,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 4,57</t>
+          <t>-11,66; 5,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 7,14</t>
+          <t>-10,72; 7,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 8,76</t>
+          <t>-4,94; 8,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 5,53</t>
+          <t>-7,49; 5,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 5,01</t>
+          <t>-8,82; 4,0</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,53; 126,07</t>
+          <t>-81,12; 116,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 248,69</t>
+          <t>-58,82; 304,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 225,64</t>
+          <t>-77,06; 233,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 348,73</t>
+          <t>-30,89; 356,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,49; 102,09</t>
+          <t>-80,62; 174,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 155,89</t>
+          <t>-74,34; 185,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 143,27</t>
+          <t>-39,69; 128,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 93,88</t>
+          <t>-58,06; 78,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 84,36</t>
+          <t>-67,39; 71,06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -0,26</t>
+          <t>-12,13; -0,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -1,79</t>
+          <t>-13,1; -1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 0,61</t>
+          <t>-12,39; 0,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,31</t>
+          <t>-9,21; 2,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 4,53</t>
+          <t>-8,01; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 1,88</t>
+          <t>-8,81; 2,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,26</t>
+          <t>-8,27; 0,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 0,24</t>
+          <t>-8,71; -0,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -0,29</t>
+          <t>-8,61; -0,31</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,61; 11,97</t>
+          <t>-87,26; 7,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-91,98; -7,05</t>
+          <t>-93,34; -1,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 18,08</t>
+          <t>-86,6; 16,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 72,12</t>
+          <t>-80,41; 57,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 94,47</t>
+          <t>-71,65; 87,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,84; 60,99</t>
+          <t>-81,83; 74,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 16,21</t>
+          <t>-74,27; 5,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 5,49</t>
+          <t>-72,41; -0,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-74,9; -2,26</t>
+          <t>-76,08; -2,92</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 6,52</t>
+          <t>-6,6; 6,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 1,49</t>
+          <t>-9,12; 1,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,88</t>
+          <t>-0,54; 16,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,6</t>
+          <t>-1,72; 7,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,1</t>
+          <t>-4,2; 2,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 13,04</t>
+          <t>0,99; 12,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,08</t>
+          <t>-2,74; 5,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,69</t>
+          <t>-5,52; 0,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 11,63</t>
+          <t>1,54; 12,06</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 848,92</t>
+          <t>-25,77; 1024,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,92; —</t>
+          <t>-62,36; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,53; 323,21</t>
+          <t>-58,35; 376,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 212,85</t>
+          <t>-100,0; 121,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,82; 707,06</t>
+          <t>15,11; 930,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 7,95</t>
+          <t>-5,63; 8,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 15,93</t>
+          <t>-0,12; 16,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -0,13</t>
+          <t>-11,64; -0,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 8,75</t>
+          <t>-0,45; 8,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,53</t>
+          <t>3,31; 17,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,45</t>
+          <t>-4,58; 1,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,56</t>
+          <t>-1,03; 6,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,87</t>
+          <t>3,58; 14,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,01</t>
+          <t>-5,94; -0,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,45; 284,89</t>
+          <t>-57,62; 290,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 537,8</t>
+          <t>-14,91; 480,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 72,26</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 300,15</t>
+          <t>-29,02; 351,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,96; 605,61</t>
+          <t>48,92; 727,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 52,69</t>
+          <t>-100,0; 77,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 13,75</t>
+          <t>-8,63; 12,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,9; -0,65</t>
+          <t>-16,86; -0,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 12,58</t>
+          <t>-9,28; 11,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 10,31</t>
+          <t>-12,38; 9,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 1,04</t>
+          <t>-18,43; 0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 4,2</t>
+          <t>-17,19; 3,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 7,69</t>
+          <t>-8,78; 7,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -1,91</t>
+          <t>-14,38; -1,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 5,36</t>
+          <t>-8,51; 5,67</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 536,72</t>
+          <t>-69,1; 346,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,44 +1657,44 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,23; 433,0</t>
+          <t>-74,23; 356,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 178,42</t>
+          <t>-71,38; 211,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,98; 102,74</t>
+          <t>-85,81; 91,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-57,71; 107,71</t>
+          <t>-60,26; 111,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-93,56; 3,2</t>
+          <t>-93,94; -8,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,15; 87,32</t>
+          <t>-63,12; 98,33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 11,02</t>
+          <t>-3,61; 10,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,27; 19,05</t>
+          <t>0,7; 18,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 7,8</t>
+          <t>-5,58; 8,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 14,03</t>
+          <t>-6,32; 13,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 6,63</t>
+          <t>-10,91; 5,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 1,15</t>
+          <t>-13,51; 0,8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 9,4</t>
+          <t>-2,38; 10,22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 9,31</t>
+          <t>-2,82; 9,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 2,32</t>
+          <t>-7,5; 3,0</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 1270,21</t>
+          <t>-22,17; 1452,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,39 +1878,39 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-45,83; 358,78</t>
+          <t>-50,96; 294,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-85,56; 176,36</t>
+          <t>-85,03; 123,85</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,27</t>
+          <t>-100,0; 61,53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 229,98</t>
+          <t>-35,92; 250,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 230,72</t>
+          <t>-37,23; 229,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-86,11; 71,15</t>
+          <t>-82,32; 95,88</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 6,2</t>
+          <t>-2,81; 5,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 4,1</t>
+          <t>-4,0; 4,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,64; 10,74</t>
+          <t>0,29; 11,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 3,79</t>
+          <t>-6,5; 3,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -1,35</t>
+          <t>-9,89; -1,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,55</t>
+          <t>-3,81; 7,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,36</t>
+          <t>-3,65; 3,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,22</t>
+          <t>-5,7; 0,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 7,59</t>
+          <t>-0,22; 7,66</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 307,63</t>
+          <t>-57,34; 297,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,24; 215,2</t>
+          <t>-67,45; 219,56</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 530,73</t>
+          <t>-4,68; 545,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-73,26; 93,13</t>
+          <t>-69,01; 75,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,61</t>
+          <t>-95,55; -6,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,55; 175,43</t>
+          <t>-41,14; 164,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 83,25</t>
+          <t>-49,72; 90,46</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-77,02; 9,57</t>
+          <t>-74,71; 18,94</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 188,35</t>
+          <t>-4,66; 197,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -0,56</t>
+          <t>-9,85; -1,14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 1,63</t>
+          <t>-8,41; 1,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -3,06</t>
+          <t>-11,47; -2,97</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,43; -0,25</t>
+          <t>-9,03; -0,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -0,93</t>
+          <t>-9,95; -0,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,21; -4,11</t>
+          <t>-12,19; -4,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,21; -1,97</t>
+          <t>-8,23; -1,81</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -0,96</t>
+          <t>-8,03; -1,37</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,72; -4,55</t>
+          <t>-10,5; -4,78</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-80,05; -4,45</t>
+          <t>-81,62; -9,32</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 30,15</t>
+          <t>-73,01; 22,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,48</t>
+          <t>-94,34; -32,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-75,96; -2,17</t>
+          <t>-75,64; -0,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-78,77; -7,33</t>
+          <t>-80,13; -4,61</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-95,51; -47,81</t>
+          <t>-95,9; -46,71</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-73,56; -25,39</t>
+          <t>-72,42; -19,7</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-68,83; -9,87</t>
+          <t>-70,42; -16,11</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-93,82; -56,26</t>
+          <t>-93,36; -59,42</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,76</t>
+          <t>-3,96; 0,49</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,29</t>
+          <t>-3,2; 1,5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,11</t>
+          <t>-3,52; 1,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,86</t>
+          <t>-2,59; 1,92</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,19</t>
+          <t>-4,44; -0,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,15</t>
+          <t>-4,5; -0,21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,66</t>
+          <t>-2,46; 0,66</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,23</t>
+          <t>-3,19; -0,0</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,11</t>
+          <t>-3,38; -0,18</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 13,39</t>
+          <t>-47,71; 7,83</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 21,72</t>
+          <t>-36,57; 27,92</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 17,79</t>
+          <t>-41,86; 19,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 32,18</t>
+          <t>-31,11; 29,8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-54,09; -2,18</t>
+          <t>-52,49; -2,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 3,16</t>
+          <t>-53,73; -2,18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 10,09</t>
+          <t>-30,91; 10,48</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-40,37; -3,14</t>
+          <t>-40,41; 0,01</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -1,49</t>
+          <t>-41,82; -2,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 4,98</t>
+          <t>-12,57; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 11,76</t>
+          <t>-8,53; 10,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 8,55</t>
+          <t>-11,9; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 16,54</t>
+          <t>-3,19; 16,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 5,77</t>
+          <t>-12,65; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 7,57</t>
+          <t>-11,02; 7,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 8,85</t>
+          <t>-5,44; 8,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 5,07</t>
+          <t>-7,47; 5,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 4,0</t>
+          <t>-8,31; 5,14</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,12; 116,46</t>
+          <t>-83,42; 119,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 304,82</t>
+          <t>-62,22; 210,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,06; 233,71</t>
+          <t>-77,74; 167,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 356,48</t>
+          <t>-29,04; 339,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,62; 174,03</t>
+          <t>-87,22; 124,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,34; 185,11</t>
+          <t>-77,63; 172,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 128,82</t>
+          <t>-42,92; 144,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 78,81</t>
+          <t>-55,46; 95,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 71,06</t>
+          <t>-63,66; 91,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,13; -0,23</t>
+          <t>-11,94; -0,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -1,42</t>
+          <t>-12,2; -2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 0,38</t>
+          <t>-12,94; 0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 2,78</t>
+          <t>-8,06; 3,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 4,33</t>
+          <t>-6,67; 5,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,6</t>
+          <t>-9,03; 2,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 0,07</t>
+          <t>-7,97; -0,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -0,32</t>
+          <t>-7,65; 0,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,61; -0,31</t>
+          <t>-8,18; -0,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,26; 7,09</t>
+          <t>-87,32; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-93,34; -1,14</t>
+          <t>-93,49; -20,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,6; 16,93</t>
+          <t>-89,28; 8,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 57,7</t>
+          <t>-72,86; 89,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 87,56</t>
+          <t>-61,57; 119,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,83; 74,44</t>
+          <t>-82,36; 78,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,27; 5,01</t>
+          <t>-72,28; 2,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,41; -0,85</t>
+          <t>-71,41; 6,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-76,08; -2,92</t>
+          <t>-75,47; 2,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 6,69</t>
+          <t>-6,17; 5,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 1,4</t>
+          <t>-8,33; 1,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 16,11</t>
+          <t>-0,36; 15,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 7,44</t>
+          <t>-1,73; 7,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 2,13</t>
+          <t>-3,76; 2,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 12,97</t>
+          <t>0,3; 12,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,34</t>
+          <t>-2,86; 4,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,71</t>
+          <t>-5,46; 0,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,06</t>
+          <t>1,14; 11,57</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 1024,1</t>
+          <t>-20,99; 935,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,36; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 376,17</t>
+          <t>-59,22; 336,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,66</t>
+          <t>-100,0; 121,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,11; 930,93</t>
+          <t>5,28; 708,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 8,39</t>
+          <t>-5,59; 8,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 16,25</t>
+          <t>0,24; 16,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -0,31</t>
+          <t>-11,08; -0,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 8,94</t>
+          <t>-0,25; 8,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 17,31</t>
+          <t>3,61; 16,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,41</t>
+          <t>-4,18; 1,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 6,78</t>
+          <t>-1,2; 7,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 14,07</t>
+          <t>3,46; 13,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,94; -0,08</t>
+          <t>-5,95; -0,08</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,62; 290,24</t>
+          <t>-59,53; 288,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 480,65</t>
+          <t>-11,17; 485,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,26</t>
+          <t>-100,0; 222,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 351,54</t>
+          <t>-31,28; 333,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,92; 727,86</t>
+          <t>43,79; 687,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,22</t>
+          <t>-100,0; 65,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 12,2</t>
+          <t>-8,95; 12,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -0,41</t>
+          <t>-17,16; -1,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 11,8</t>
+          <t>-8,57; 13,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 9,91</t>
+          <t>-13,15; 9,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 0,25</t>
+          <t>-18,18; 0,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 3,83</t>
+          <t>-15,66; 3,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 7,46</t>
+          <t>-7,56; 8,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,38; -1,21</t>
+          <t>-14,46; -1,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 5,67</t>
+          <t>-8,88; 5,69</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,1; 346,39</t>
+          <t>-74,43; 333,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,23; 356,37</t>
+          <t>-66,09; 443,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 211,51</t>
+          <t>-72,23; 171,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,65; 52,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,81; 91,64</t>
+          <t>-85,33; 103,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-60,26; 111,34</t>
+          <t>-51,59; 138,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-93,94; -8,71</t>
+          <t>-94,08; -10,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 98,33</t>
+          <t>-64,16; 86,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 10,7</t>
+          <t>-4,51; 10,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,7; 18,54</t>
+          <t>0,94; 18,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 8,97</t>
+          <t>-4,93; 8,56</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 13,72</t>
+          <t>-6,46; 13,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 5,1</t>
+          <t>-12,4; 4,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 0,8</t>
+          <t>-13,71; 0,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 10,22</t>
+          <t>-2,5; 9,65</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 9,42</t>
+          <t>-2,91; 9,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 3,0</t>
+          <t>-7,64; 1,99</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 1452,22</t>
+          <t>-20,59; 1362,72</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 294,81</t>
+          <t>-53,21; 292,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-85,03; 123,85</t>
+          <t>-89,88; 101,68</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,53</t>
+          <t>-95,13; 75,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 250,08</t>
+          <t>-34,67; 244,62</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 229,36</t>
+          <t>-35,92; 218,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,32; 95,88</t>
+          <t>-82,43; 62,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,94</t>
+          <t>-3,04; 6,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 4,21</t>
+          <t>-4,06; 4,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,29; 11,52</t>
+          <t>0,45; 11,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 3,29</t>
+          <t>-6,75; 3,64</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -1,05</t>
+          <t>-9,72; -1,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,76</t>
+          <t>-4,42; 7,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,47</t>
+          <t>-3,28; 3,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,25</t>
+          <t>-5,49; 0,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 7,66</t>
+          <t>-0,36; 7,76</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 297,68</t>
+          <t>-55,69; 293,58</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,45; 219,56</t>
+          <t>-67,92; 190,21</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 545,01</t>
+          <t>-8,13; 590,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 75,86</t>
+          <t>-70,32; 82,94</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-95,55; -6,09</t>
+          <t>-94,76; -4,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,14; 164,35</t>
+          <t>-47,35; 152,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-49,72; 90,46</t>
+          <t>-47,28; 77,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 18,94</t>
+          <t>-75,79; 10,04</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 197,49</t>
+          <t>-8,22; 185,13</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -1,14</t>
+          <t>-9,42; -0,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 1,29</t>
+          <t>-8,36; 1,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,47; -2,97</t>
+          <t>-11,7; -3,3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,03; -0,17</t>
+          <t>-9,25; -0,57</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -0,7</t>
+          <t>-9,6; -0,69</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,19; -4,0</t>
+          <t>-12,06; -3,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -1,81</t>
+          <t>-8,23; -1,9</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -1,37</t>
+          <t>-7,69; -1,07</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -4,78</t>
+          <t>-10,57; -4,48</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-81,62; -9,32</t>
+          <t>-79,77; -8,18</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-73,01; 22,55</t>
+          <t>-71,72; 26,5</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-94,34; -32,44</t>
+          <t>-95,62; -34,41</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-75,64; -0,66</t>
+          <t>-75,33; 2,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-80,13; -4,61</t>
+          <t>-78,69; -2,18</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-95,9; -46,71</t>
+          <t>-95,53; -37,31</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-72,42; -19,7</t>
+          <t>-73,01; -24,9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-70,42; -16,11</t>
+          <t>-68,46; -11,81</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-93,36; -59,42</t>
+          <t>-92,56; -56,88</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,49</t>
+          <t>-3,85; 0,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,5</t>
+          <t>-3,12; 1,38</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,11</t>
+          <t>-3,55; 0,99</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,92</t>
+          <t>-2,55; 1,92</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,44; -0,26</t>
+          <t>-4,59; -0,35</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,21</t>
+          <t>-4,43; -0,03</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,66</t>
+          <t>-2,59; 0,65</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,0</t>
+          <t>-3,21; -0,07</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,18</t>
+          <t>-3,4; -0,18</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 7,83</t>
+          <t>-46,26; 9,04</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 27,92</t>
+          <t>-38,22; 23,18</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 19,28</t>
+          <t>-43,62; 16,33</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 29,8</t>
+          <t>-30,37; 30,76</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-52,49; -2,5</t>
+          <t>-53,54; -5,19</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -2,18</t>
+          <t>-53,64; 0,07</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 10,48</t>
+          <t>-32,53; 9,75</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 0,01</t>
+          <t>-39,69; -0,41</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -2,1</t>
+          <t>-42,41; -2,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,46</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 4,78</t>
+          <t>-3,16; 16,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 10,64</t>
+          <t>-12,54; 4,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 6,73</t>
+          <t>-10,57; 8,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 16,6</t>
+          <t>-12,02; 5,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 5,4</t>
+          <t>-7,95; 11,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 7,22</t>
+          <t>-11,33; 5,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 8,8</t>
+          <t>-4,78; 8,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 5,4</t>
+          <t>-7,48; 5,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 5,14</t>
+          <t>-8,33; 4,82</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>65,61%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-35,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-9,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-31,46%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>15,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-21,24%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65,61%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-35,28%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-17,35%</t>
+          <t>-28,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-19,25%</t>
+          <t>-18,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 119,64</t>
+          <t>-26,65; 348,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 210,47</t>
+          <t>-87,49; 102,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,74; 167,65</t>
+          <t>-74,76; 180,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 339,4</t>
+          <t>-81,53; 126,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,22; 124,71</t>
+          <t>-56,56; 248,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,63; 172,26</t>
+          <t>-78,21; 175,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 144,56</t>
+          <t>-38,75; 143,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 95,06</t>
+          <t>-57,59; 93,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,66; 91,64</t>
+          <t>-65,72; 70,58</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,18</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-5,87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-7,12</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,5</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-3,98</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,56</t>
+          <t>-3,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -0,4</t>
+          <t>-8,97; 3,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; -2,09</t>
+          <t>-6,78; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 0,35</t>
+          <t>-8,83; 1,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 3,69</t>
+          <t>-11,88; -0,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 5,13</t>
+          <t>-13,48; -1,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 2,01</t>
+          <t>-10,91; 2,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -0,07</t>
+          <t>-8,03; 0,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,26</t>
+          <t>-7,86; 0,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; -0,06</t>
+          <t>-7,79; 0,42</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-31,73%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-14,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-47,7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-58,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-70,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-54,71%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-31,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-14,61%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-45,99%</t>
+          <t>-39,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-50,53%</t>
+          <t>-43,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,32; 3,02</t>
+          <t>-79,6; 72,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-93,49; -20,27</t>
+          <t>-64,07; 94,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,28; 8,94</t>
+          <t>-82,35; 58,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,86; 89,29</t>
+          <t>-85,61; 11,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 119,8</t>
+          <t>-91,98; -7,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,36; 78,93</t>
+          <t>-80,48; 50,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,28; 2,67</t>
+          <t>-70,68; 16,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,41; 6,33</t>
+          <t>-71,81; 5,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-75,47; 2,43</t>
+          <t>-71,23; 7,5</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,41</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,35</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,98</t>
+          <t>-1,85; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 1,68</t>
+          <t>-4,54; 2,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 15,37</t>
+          <t>0,84; 12,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 7,63</t>
+          <t>-5,98; 6,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,06</t>
+          <t>-8,41; 1,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 12,98</t>
+          <t>0,09; 15,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,95</t>
+          <t>-2,72; 5,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,72</t>
+          <t>-5,48; 0,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,57</t>
+          <t>1,63; 11,48</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>121,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-45,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>289,36%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,79%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-71,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149,67%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>121,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-45,61%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>312,22%</t>
+          <t>150,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>193,85%</t>
+          <t>190,38%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 935,37</t>
+          <t>-54,37; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,35; 856,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 336,94</t>
+          <t>-56,53; 323,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,86</t>
+          <t>-100,0; 212,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 708,1</t>
+          <t>15,66; 715,7</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,56</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,66</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-5,25</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,56</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,5</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-2,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 8,25</t>
+          <t>-0,33; 8,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 16,7</t>
+          <t>3,41; 15,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,08; -0,06</t>
+          <t>-4,31; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 8,67</t>
+          <t>-6,0; 7,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 16,0</t>
+          <t>-0,74; 15,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,55</t>
+          <t>-11,09; -0,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 7,11</t>
+          <t>-1,39; 6,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,68</t>
+          <t>3,19; 13,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -0,08</t>
+          <t>-5,94; 0,03</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>330,44%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>812,52%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-38,42%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>21,21%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>115,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-79,55%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>330,44%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>812,52%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-33,28%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>67,35%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-72,67%</t>
+          <t>-73,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 288,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 485,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 222,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>-57,45; 284,89</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-9,21; 537,8</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 333,88</t>
+          <t>-32,47; 300,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,79; 687,08</t>
+          <t>36,96; 605,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 65,53</t>
+          <t>-100,0; 49,31</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-7,76</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,79</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-7,07</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-7,76</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 12,7</t>
+          <t>-12,39; 10,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,16; -1,61</t>
+          <t>-18,37; 1,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 13,25</t>
+          <t>-16,31; 4,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 9,3</t>
+          <t>-8,51; 13,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 0,78</t>
+          <t>-15,9; -0,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 3,89</t>
+          <t>-7,82; 13,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 8,56</t>
+          <t>-8,16; 7,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,46; -1,85</t>
+          <t>-14,71; -1,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 5,69</t>
+          <t>-9,23; 5,99</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-9,92%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-63,7%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-39,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-82,16%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-9,92%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-63,7%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-43,22%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-18,22%</t>
+          <t>-13,72%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,43; 333,87</t>
+          <t>-72,35; 178,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 66,69</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-83,86; 113,01</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-67,74; 536,72</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>-66,09; 443,46</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-72,23; 171,83</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-92,65; 52,13</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,33; 103,61</t>
+          <t>-60,54; 461,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 138,36</t>
+          <t>-57,71; 107,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-94,08; -10,75</t>
+          <t>-93,56; 3,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 86,45</t>
+          <t>-60,33; 95,21</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,36</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-3,21</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-6,15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,21</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>9,26</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-3,21</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,76</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 10,68</t>
+          <t>-5,24; 14,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,94; 18,77</t>
+          <t>-10,87; 6,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 8,56</t>
+          <t>-14,73; 0,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 13,5</t>
+          <t>-3,43; 11,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 4,81</t>
+          <t>1,27; 19,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 0,86</t>
+          <t>-4,77; 7,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 9,65</t>
+          <t>-3,35; 9,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 9,07</t>
+          <t>-3,02; 9,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 1,99</t>
+          <t>-7,98; 2,01</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>37,02%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-35,39%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-67,74%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>58,52%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>244,92%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-35,39%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-63,49%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-39,68%</t>
+          <t>-41,09%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-45,83; 358,78</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-85,56; 176,36</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 57,1</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>-20,59; 1362,72</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-12,05; 1270,21</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-53,21; 292,47</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-89,88; 101,68</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-95,13; 75,27</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 244,62</t>
+          <t>-42,75; 229,98</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 218,28</t>
+          <t>-39,36; 230,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,43; 62,28</t>
+          <t>-85,08; 74,75</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-5,23</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1,95</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,23</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-5,23</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>3,96</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,11</t>
+          <t>-6,67; 3,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 4,02</t>
+          <t>-9,72; -1,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 11,71</t>
+          <t>-3,49; 8,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,64</t>
+          <t>-2,94; 6,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -1,19</t>
+          <t>-3,96; 4,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 7,4</t>
+          <t>0,97; 11,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,31</t>
+          <t>-3,44; 3,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,16</t>
+          <t>-5,57; 0,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,76</t>
+          <t>-0,08; 8,21</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-21,15%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-74,61%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>30,34%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>138,33%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-21,15%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-74,61%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>150,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,69; 293,58</t>
+          <t>-73,26; 93,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,92; 190,21</t>
+          <t>-100,0; -3,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 590,96</t>
+          <t>-40,37; 181,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 82,94</t>
+          <t>-54,51; 307,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-94,76; -4,61</t>
+          <t>-67,24; 215,2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 152,16</t>
+          <t>5,63; 568,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 77,38</t>
+          <t>-50,58; 83,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 10,04</t>
+          <t>-77,02; 9,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 185,13</t>
+          <t>-1,92; 209,2</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-4,68</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-5,15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-7,96</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-4,98</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-3,58</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-7,11</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-4,68</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-5,15</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-7,89</t>
+          <t>-7,05</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,42; -0,82</t>
+          <t>-9,43; -0,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,19</t>
+          <t>-9,75; -0,93</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -3,3</t>
+          <t>-12,32; -4,23</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,25; -0,57</t>
+          <t>-9,41; -0,56</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -0,69</t>
+          <t>-8,21; 1,63</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -3,93</t>
+          <t>-11,57; -2,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -1,9</t>
+          <t>-8,21; -1,97</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,69; -1,07</t>
+          <t>-7,62; -0,96</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,57; -4,48</t>
+          <t>-10,73; -4,52</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-49,39%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-54,33%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-83,98%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-55,69%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-40,05%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-79,49%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-49,39%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-54,33%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-83,24%</t>
+          <t>-78,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-81,55%</t>
+          <t>-81,6%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-79,77; -8,18</t>
+          <t>-75,96; -2,17</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-71,72; 26,5</t>
+          <t>-78,77; -7,33</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-95,62; -34,41</t>
+          <t>-95,88; -50,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 2,14</t>
+          <t>-80,05; -4,45</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-78,69; -2,18</t>
+          <t>-69,64; 30,15</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -37,31</t>
+          <t>-100,0; -27,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -24,9</t>
+          <t>-73,56; -25,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-68,46; -11,81</t>
+          <t>-68,83; -9,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-92,56; -56,88</t>
+          <t>-93,88; -57,74</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-2,47</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,89</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,66</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,52</t>
+          <t>-2,62; 1,86</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,38</t>
+          <t>-4,54; -0,19</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,99</t>
+          <t>-4,32; 0,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,92</t>
+          <t>-3,76; 0,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -0,35</t>
+          <t>-3,15; 1,29</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,03</t>
+          <t>-3,29; 1,37</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,65</t>
+          <t>-2,57; 0,66</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,07</t>
+          <t>-3,23; -0,23</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,18</t>
+          <t>-3,25; -0,03</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-4,85%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-33,93%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-31,66%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-22,12%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-12,54%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-16,64%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-4,85%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-33,93%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-31,07%</t>
+          <t>-13,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-24,38%</t>
+          <t>-23,0%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 9,04</t>
+          <t>-31,7; 32,18</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 23,18</t>
+          <t>-54,09; -2,18</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 16,33</t>
+          <t>-52,1; 1,51</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 30,76</t>
+          <t>-45,78; 13,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-53,54; -5,19</t>
+          <t>-39,31; 21,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 0,07</t>
+          <t>-39,33; 23,26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 9,75</t>
+          <t>-31,82; 10,09</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -0,41</t>
+          <t>-40,37; -3,14</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -2,52</t>
+          <t>-40,37; 0,26</t>
         </is>
       </c>
     </row>
